--- a/results/05-2026/beta/contributions-05-2026.xlsx
+++ b/results/05-2026/beta/contributions-05-2026.xlsx
@@ -3036,7 +3036,7 @@
         <v>-0.0000531438557844164</v>
       </c>
       <c r="W25" t="n">
-        <v>0.338301811894314</v>
+        <v>0.283001238493291</v>
       </c>
       <c r="X25" t="n">
         <v>0.0427711776553399</v>
@@ -3051,22 +3051,22 @@
         <v>-0.270169588737866</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.408480143900867</v>
+        <v>0.353220653663715</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.139473515989945</v>
+        <v>0.0840566015320863</v>
       </c>
       <c r="AD25" t="n">
         <v>-0.412652726526158</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.432744756378526</v>
+        <v>0.377485266141373</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.17826914678364</v>
+        <v>-1.2336860612415</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.49086414168114</v>
+        <v>-0.504718370295605</v>
       </c>
     </row>
     <row r="26">
@@ -3137,7 +3137,7 @@
         <v>-0.0000696617484409661</v>
       </c>
       <c r="W26" t="n">
-        <v>0.279329039690738</v>
+        <v>0.224985702190415</v>
       </c>
       <c r="X26" t="n">
         <v>0.0124692193307716</v>
@@ -3152,22 +3152,22 @@
         <v>0.463404670727734</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.00467134528318946</v>
+        <v>-0.059175626483968</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.518755843342824</v>
+        <v>0.464514269397324</v>
       </c>
       <c r="AD26" t="n">
         <v>0.148888893636348</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.00341842784719892</v>
+        <v>-0.0579227090479775</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.884206322384365</v>
+        <v>0.829964748438865</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.103496105815382</v>
+        <v>-0.130910727916221</v>
       </c>
     </row>
     <row r="27">
@@ -3238,10 +3238,10 @@
         <v>-0.000501429966115183</v>
       </c>
       <c r="W27" t="n">
-        <v>0.247504863679855</v>
+        <v>0.207022102238222</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0487650643212487</v>
+        <v>0.0365288260044681</v>
       </c>
       <c r="Y27" t="n">
         <v>-0.330545226387455</v>
@@ -3253,22 +3253,22 @@
         <v>0.485607963229528</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.0416926751894501</v>
+        <v>-0.0111200504906592</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.587088193681598</v>
+        <v>0.534544569658873</v>
       </c>
       <c r="AD27" t="n">
         <v>0.234064323299038</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.0447763327104476</v>
+        <v>-0.00803639296966173</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.163659314276233</v>
+        <v>0.111115690253508</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.0398941382049361</v>
+        <v>-0.000656389901584911</v>
       </c>
     </row>
     <row r="28">
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.146342913256379</v>
+        <v>-0.30586383600656</v>
       </c>
       <c r="E28" t="n">
         <v>-0.176236422781678</v>
@@ -3339,13 +3339,13 @@
         <v>-0.000426940925803921</v>
       </c>
       <c r="W28" t="n">
-        <v>0.200762093320125</v>
+        <v>0.162770134174828</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.0141682460370789</v>
+        <v>-0.0273950236581683</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.182706291067979</v>
+        <v>-0.34222721381816</v>
       </c>
       <c r="Z28" t="n">
         <v>-0.139873044970078</v>
@@ -3354,22 +3354,22 @@
         <v>0.255014185511323</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.128159277609808</v>
+        <v>0.0769259524623977</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.442829230353156</v>
+        <v>0.391733535269023</v>
       </c>
       <c r="AD28" t="n">
         <v>0.177083575542115</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.123898637736446</v>
+        <v>0.0726653125890352</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.120249894315099</v>
+        <v>-0.0903667235192149</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.00253840395198553</v>
+        <v>-0.095743086517085</v>
       </c>
     </row>
     <row r="29">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.10687586310228</v>
+        <v>-0.106184459909413</v>
       </c>
       <c r="E29" t="n">
         <v>-0.199946813675512</v>
@@ -3440,13 +3440,13 @@
         <v>-0.000395175505607586</v>
       </c>
       <c r="W29" t="n">
-        <v>0.164055586793484</v>
+        <v>0.110104285704918</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0153627081459999</v>
+        <v>-0.0142421131305181</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.165982905043573</v>
+        <v>-0.165291501850706</v>
       </c>
       <c r="Z29" t="n">
         <v>-0.140839771734219</v>
@@ -3455,22 +3455,22 @@
         <v>-0.0600454191026175</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.17980531124795</v>
+        <v>0.0962927443821378</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.179873938990407</v>
+        <v>0.096308392813431</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.00775380490190472</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.171173759027019</v>
+        <v>0.0876611921612072</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.126948737787385</v>
+        <v>-0.209822880771494</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.260291698297078</v>
+        <v>0.160222708600416</v>
       </c>
     </row>
     <row r="30">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.11397551834177</v>
+        <v>-0.113238185935717</v>
       </c>
       <c r="E30" t="n">
         <v>-0.186214773942108</v>
@@ -3541,13 +3541,13 @@
         <v>-0.000365697253103981</v>
       </c>
       <c r="W30" t="n">
-        <v>0.125233288715792</v>
+        <v>0.0747419360682316</v>
       </c>
       <c r="X30" t="n">
-        <v>0.0224941043379145</v>
+        <v>-0.00432257924151644</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.1602387861888</v>
+        <v>-0.159501453782747</v>
       </c>
       <c r="Z30" t="n">
         <v>-0.139951506095078</v>
@@ -3556,22 +3556,22 @@
         <v>-0.533901846857373</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.264760058414852</v>
+        <v>0.18758138864818</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.207644369916542</v>
+        <v>-0.285259688698547</v>
       </c>
       <c r="AD30" t="n">
         <v>-0.267027899335481</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.262385836880811</v>
+        <v>0.18520716711414</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.50783466220042</v>
+        <v>-0.584712648576373</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.0877185478491185</v>
+        <v>-0.193446640653394</v>
       </c>
     </row>
     <row r="31">
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0975287813488231</v>
+        <v>-0.0968978464598438</v>
       </c>
       <c r="E31" t="n">
         <v>-0.18074145350152</v>
@@ -3642,13 +3642,13 @@
         <v>-0.000318458448563437</v>
       </c>
       <c r="W31" t="n">
-        <v>0.119159394811257</v>
+        <v>0.0602243053891414</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.00107466719411561</v>
+        <v>-0.0135877228904138</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.14208312752099</v>
+        <v>-0.14145219263201</v>
       </c>
       <c r="Z31" t="n">
         <v>-0.136187107329353</v>
@@ -3657,22 +3657,22 @@
         <v>-0.484036400696089</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.142418793573071</v>
+        <v>0.0709964759778335</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.280885780310953</v>
+        <v>-0.352675151673145</v>
       </c>
       <c r="AD31" t="n">
         <v>-0.120213984396549</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.142742647755256</v>
+        <v>0.0713203301600185</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.559156015161296</v>
+        <v>-0.630314451634508</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.268422380208501</v>
+        <v>-0.378804176125398</v>
       </c>
     </row>
     <row r="32">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.104154696248239</v>
+        <v>-0.103480896875323</v>
       </c>
       <c r="E32" t="n">
         <v>-0.188023408655981</v>
@@ -3743,13 +3743,13 @@
         <v>-0.000312156590467466</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0652367227493609</v>
+        <v>0.0092716635034082</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.0134946507383032</v>
+        <v>-0.0234751031805249</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.147016752572777</v>
+        <v>-0.146342953199862</v>
       </c>
       <c r="Z32" t="n">
         <v>-0.145161352331443</v>
@@ -3758,22 +3758,22 @@
         <v>-0.260600449467441</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.0804088679384772</v>
+        <v>0.0144763954096759</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.179969244932549</v>
+        <v>-0.246084030405244</v>
       </c>
       <c r="AD32" t="n">
         <v>0.125828825912292</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.0753714824875317</v>
+        <v>0.00943900995873045</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.472147349836769</v>
+        <v>-0.537588335936549</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.416521691246468</v>
+        <v>-0.490609579229731</v>
       </c>
     </row>
     <row r="33">
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.171995982760397</v>
+        <v>-0.170883303356563</v>
       </c>
       <c r="E33" t="n">
         <v>-0.184495417794735</v>
@@ -3844,13 +3844,13 @@
         <v>-0.000305491844496977</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0239552259170439</v>
+        <v>-0.00136295384642158</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.00000458810015208636</v>
+        <v>-0.0115869753952157</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.213430042513555</v>
+        <v>-0.212317363109721</v>
       </c>
       <c r="Z33" t="n">
         <v>-0.143061358041577</v>
@@ -3859,22 +3859,22 @@
         <v>-0.247370645122349</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.02383117359416</v>
+        <v>-0.0130696093021457</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.223476852791337</v>
+        <v>-0.260474593853452</v>
       </c>
       <c r="AD33" t="n">
         <v>0.181346316904211</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.0198902270893699</v>
+        <v>-0.0170105558069359</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.579968253346469</v>
+        <v>-0.615853315004751</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.529776570136239</v>
+        <v>-0.592117187788045</v>
       </c>
     </row>
     <row r="34">
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.205141427200942</v>
+        <v>-0.203814322711313</v>
       </c>
       <c r="E34" t="n">
         <v>-0.183578043716544</v>
@@ -3945,13 +3945,13 @@
         <v>-0.000299428155345378</v>
       </c>
       <c r="W34" t="n">
-        <v>0.00302249226130404</v>
+        <v>-0.0331773637149976</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0216035681134529</v>
+        <v>0.00776152455226643</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.245538348742651</v>
+        <v>-0.244211244253022</v>
       </c>
       <c r="Z34" t="n">
         <v>-0.143181122174836</v>
@@ -3960,22 +3960,22 @@
         <v>-0.59681672518361</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.0527204838840258</v>
+        <v>-0.10280007135667</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.649871055737251</v>
+        <v>-0.700267708903581</v>
       </c>
       <c r="AD34" t="n">
         <v>0.0200594465950505</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.0527204838840258</v>
+        <v>-0.10280007135667</v>
       </c>
       <c r="AF34" t="n">
-        <v>-1.03859052665474</v>
+        <v>-1.08766007533144</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.662465536249818</v>
+        <v>-0.717854044476812</v>
       </c>
     </row>
   </sheetData>

--- a/results/05-2026/beta/contributions-05-2026.xlsx
+++ b/results/05-2026/beta/contributions-05-2026.xlsx
@@ -751,7 +751,7 @@
         <v>0.0488379551020667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0128552657625797</v>
+        <v>0.104919497398701</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -805,22 +805,22 @@
         <v>-2.39722668676711</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.218260041490563</v>
+        <v>0.310013322726237</v>
       </c>
       <c r="AA3" t="n">
         <v>8.6385202038646</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.82499612592057</v>
+        <v>8.90337703978357</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.218260041490563</v>
+        <v>0.310013322726237</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.2647047682737</v>
+        <v>10.3430856821367</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.98312735601048</v>
+        <v>3.00272258447623</v>
       </c>
     </row>
     <row r="4">
@@ -846,7 +846,7 @@
         <v>0.0790187713359683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0143221335174119</v>
+        <v>0.239478027765301</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -900,22 +900,22 @@
         <v>-0.064635955563641</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.552346472186169</v>
+        <v>0.776553839630428</v>
       </c>
       <c r="AA4" t="n">
         <v>4.96965012385782</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.50037041244838</v>
+        <v>5.71579051059977</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.552346472186169</v>
+        <v>0.776553839630428</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.80036086375858</v>
+        <v>4.01578096190997</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.76378429164896</v>
+        <v>3.83723454465256</v>
       </c>
     </row>
     <row r="5">
@@ -941,7 +941,7 @@
         <v>-0.182435353405305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0109469268007227</v>
+        <v>0.170924495989197</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -995,22 +995,22 @@
         <v>0.0660050770494209</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.568772712361355</v>
+        <v>-0.407827476320579</v>
       </c>
       <c r="AA5" t="n">
         <v>-2.49294901262296</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.07644678264991</v>
+        <v>-2.91133777497692</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.568772712361355</v>
+        <v>-0.407827476320579</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3.34217692295723</v>
+        <v>-3.17706791528425</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.79806813571927</v>
+        <v>2.91279564064112</v>
       </c>
     </row>
     <row r="6">
@@ -1036,7 +1036,7 @@
         <v>0.040191811227022</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0146310491062612</v>
+        <v>0.164621715306164</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1090,22 +1090,22 @@
         <v>-0.572864868349367</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.193345941150108</v>
+        <v>-0.0137788292063654</v>
       </c>
       <c r="AA6" t="n">
         <v>7.81623210851637</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.63791171392507</v>
+        <v>7.80352438310025</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.193345941150108</v>
+        <v>-0.0137788292063654</v>
       </c>
       <c r="AD6" t="n">
-        <v>8.41667867412635</v>
+        <v>8.58229134330153</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.78489184580034</v>
+        <v>4.94102251801598</v>
       </c>
     </row>
     <row r="7">
@@ -1131,7 +1131,7 @@
         <v>0.0169408295689168</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0379640320507537</v>
+        <v>0.179636342636072</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1185,22 +1185,22 @@
         <v>-0.92297475522981</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.24689103402653</v>
+        <v>-0.0288747739188315</v>
       </c>
       <c r="AA7" t="n">
         <v>-1.08052926851467</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.32985687880309</v>
+        <v>-1.10968910356623</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.24689103402653</v>
+        <v>-0.0288747739188315</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.54044241633695</v>
+        <v>-2.3202746411001</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58360504964769</v>
+        <v>1.77518243720679</v>
       </c>
     </row>
     <row r="8">
@@ -1226,7 +1226,7 @@
         <v>0.0303190711719823</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0425207530530465</v>
+        <v>0.154002401080685</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1280,22 +1280,22 @@
         <v>-0.29456517846256</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.31515314337929</v>
+        <v>-0.118092063560072</v>
       </c>
       <c r="AA8" t="n">
         <v>-2.09082065057731</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.41256759108425</v>
+        <v>-2.21138431677861</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.31515314337929</v>
+        <v>-0.118092063560072</v>
       </c>
       <c r="AD8" t="n">
-        <v>-3.31812607945469</v>
+        <v>-3.11694280514905</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.196016686155632</v>
+        <v>-0.0079985045579658</v>
       </c>
     </row>
     <row r="9">
@@ -1321,7 +1321,7 @@
         <v>0.0655390793395653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0475026428300258</v>
+        <v>0.154903020368478</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1375,22 +1375,22 @@
         <v>-0.72933199543321</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.208789857580898</v>
+        <v>-0.00606153509630423</v>
       </c>
       <c r="AA9" t="n">
         <v>-2.44734167709947</v>
       </c>
       <c r="AB9" t="n">
-        <v>-2.66116289194415</v>
+        <v>-2.45354933045972</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.208789857580898</v>
+        <v>-0.00606153509630423</v>
       </c>
       <c r="AD9" t="n">
-        <v>-3.0605001913055</v>
+        <v>-2.85288662982108</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1255975032427</v>
+        <v>0.0730468168078258</v>
       </c>
     </row>
     <row r="10">
@@ -1416,7 +1416,7 @@
         <v>-0.0585793509828508</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0636914765269768</v>
+        <v>0.126940956615399</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1470,22 +1470,22 @@
         <v>-0.593660211068666</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.876075859460641</v>
+        <v>-0.683862139933784</v>
       </c>
       <c r="AA10" t="n">
         <v>-2.18260935157057</v>
       </c>
       <c r="AB10" t="n">
-        <v>-3.07814571216895</v>
+        <v>-2.88166727759111</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.876075859460641</v>
+        <v>-0.683862139933784</v>
       </c>
       <c r="AD10" t="n">
-        <v>-3.99994777750156</v>
+        <v>-3.80346934292373</v>
       </c>
       <c r="AE10" t="n">
-        <v>-3.22975411614968</v>
+        <v>-3.02339335474849</v>
       </c>
     </row>
     <row r="11">
@@ -1511,7 +1511,7 @@
         <v>-0.214664512569586</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0803342153487852</v>
+        <v>0.129024188762039</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1565,22 +1565,22 @@
         <v>-1.03787566757402</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.20568398792863</v>
+        <v>-0.993989950231089</v>
       </c>
       <c r="AA11" t="n">
         <v>-3.10202058067492</v>
       </c>
       <c r="AB11" t="n">
-        <v>-4.34461502100846</v>
+        <v>-4.12645091476793</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.20568398792863</v>
+        <v>-0.993989950231089</v>
       </c>
       <c r="AD11" t="n">
-        <v>-5.01271694177664</v>
+        <v>-4.79455283553611</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.8478227475096</v>
+        <v>-3.64196290335749</v>
       </c>
     </row>
     <row r="12">
@@ -1606,7 +1606,7 @@
         <v>0.0496954101018784</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0802162167568417</v>
+        <v>0.117940604485256</v>
       </c>
       <c r="I12" t="n">
         <v>0.0769149503246465</v>
@@ -1660,22 +1660,22 @@
         <v>0.478577805173849</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.580579627213782</v>
+        <v>-0.381400486763364</v>
       </c>
       <c r="AA12" t="n">
         <v>-1.71429964147729</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.30511780955395</v>
+        <v>-2.10242844734256</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.657494577538429</v>
+        <v>-0.458315437088011</v>
       </c>
       <c r="AD12" t="n">
-        <v>-2.44148724532298</v>
+        <v>-2.23879788311159</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.62866303897667</v>
+        <v>-3.42242667284813</v>
       </c>
     </row>
     <row r="13">
@@ -1701,7 +1701,7 @@
         <v>0.13817168563911</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0662309339104978</v>
+        <v>-0.0947484661096629</v>
       </c>
       <c r="I13" t="n">
         <v>0.0497535662897082</v>
@@ -1755,22 +1755,22 @@
         <v>0.544630454339372</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.282595033045533</v>
+        <v>-0.311177364892391</v>
       </c>
       <c r="AA13" t="n">
         <v>-0.443693965838321</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.727605922570038</v>
+        <v>-0.756321378658227</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.332348599335242</v>
+        <v>-0.360930931182099</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.450996589129198</v>
+        <v>-0.479712045217387</v>
       </c>
       <c r="AE13" t="n">
-        <v>-2.9762871384326</v>
+        <v>-2.8291330266972</v>
       </c>
     </row>
     <row r="14">
@@ -1796,7 +1796,7 @@
         <v>0.142414615890442</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.086884822835906</v>
+        <v>-0.114921618163856</v>
       </c>
       <c r="I14" t="n">
         <v>0.352688858412503</v>
@@ -1850,22 +1850,22 @@
         <v>0.323047488988425</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.818846407620433</v>
+        <v>0.791069014271982</v>
       </c>
       <c r="AA14" t="n">
         <v>-1.24218523157011</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.412958895759776</v>
+        <v>-0.441088882980743</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.46615754920793</v>
+        <v>0.43838015585948</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.152739978463895</v>
+        <v>-0.180869965684862</v>
       </c>
       <c r="AE14" t="n">
-        <v>-2.01448518867318</v>
+        <v>-1.92348318238749</v>
       </c>
     </row>
     <row r="15">
@@ -1891,7 +1891,7 @@
         <v>0.20744084444904</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0799994595193902</v>
+        <v>-0.2046841837829</v>
       </c>
       <c r="I15" t="n">
         <v>0.234874630908832</v>
@@ -1945,22 +1945,22 @@
         <v>0.37675672507515</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.762928566953573</v>
+        <v>0.639354121972862</v>
       </c>
       <c r="AA15" t="n">
         <v>-1.38234978467433</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.608293490344936</v>
+        <v>-0.733672388302574</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.528053936044742</v>
+        <v>0.404479491064031</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.500023348920457</v>
+        <v>-0.625402246878095</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.886311790459134</v>
+        <v>-0.881195535222982</v>
       </c>
     </row>
     <row r="16">
@@ -1986,7 +1986,7 @@
         <v>0.11855270408997</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.056916093561604</v>
+        <v>-0.208276940606983</v>
       </c>
       <c r="I16" t="n">
         <v>0.230313539714713</v>
@@ -2040,22 +2040,22 @@
         <v>0.600636706337094</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.412030542300483</v>
+        <v>0.261410031122298</v>
       </c>
       <c r="AA16" t="n">
         <v>-0.656622075925647</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.241770177412637</v>
+        <v>-0.393422525520161</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.18171700258577</v>
+        <v>0.0310964914075849</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.186512008878004</v>
+        <v>0.0348596607704799</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.229311976908887</v>
+        <v>-0.312781149252465</v>
       </c>
     </row>
     <row r="17">
@@ -2081,7 +2081,7 @@
         <v>0.0713566379112017</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0695617412404508</v>
+        <v>-0.208899806329515</v>
       </c>
       <c r="I17" t="n">
         <v>0.0818676169398049</v>
@@ -2135,22 +2135,22 @@
         <v>0.0879435617326674</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.168106654503534</v>
+        <v>0.0291188192368216</v>
       </c>
       <c r="AA17" t="n">
         <v>-0.662422579376793</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.493138303132385</v>
+        <v>-0.633099826986112</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0862390375637294</v>
+        <v>-0.0527487977029832</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.155168482656634</v>
+        <v>-0.29513000651036</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.155354950290746</v>
+        <v>-0.266635639575708</v>
       </c>
     </row>
     <row r="18">
@@ -2176,7 +2176,7 @@
         <v>0.226257619100136</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0583421771791422</v>
+        <v>-0.214603808595183</v>
       </c>
       <c r="I18" t="n">
         <v>0.126429969506553</v>
@@ -2224,28 +2224,28 @@
         <v>0.127457693502973</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.171780249704384</v>
+        <v>-1.32256837936611</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.110740748743783</v>
+        <v>1.26152887840551</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.78628460647213</v>
+        <v>0.631414809003844</v>
       </c>
       <c r="AA18" t="n">
         <v>-0.454576284540892</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.335478327415625</v>
+        <v>0.179865143602601</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.659854636965577</v>
+        <v>0.504984839497291</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.274438826455024</v>
+        <v>0.118825642642</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0485602490610162</v>
+        <v>-0.191711737493993</v>
       </c>
     </row>
     <row r="19">
@@ -2271,7 +2271,7 @@
         <v>0.196826924579495</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0450770336700762</v>
+        <v>-0.225123402921256</v>
       </c>
       <c r="I19" t="n">
         <v>0.0936476749635413</v>
@@ -2319,28 +2319,28 @@
         <v>0.109836183969317</v>
       </c>
       <c r="X19" t="n">
-        <v>0.166035250882516</v>
+        <v>0.176065602310738</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.045299973391732</v>
+        <v>-0.0553303248199536</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.602362580528956</v>
+        <v>0.423527566669466</v>
       </c>
       <c r="AA19" t="n">
         <v>-0.384207077760455</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.22056094924408</v>
+        <v>0.0410112570065093</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.508714905565415</v>
+        <v>0.329879891705925</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.341296226734864</v>
+        <v>0.161746534497293</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.161769644852814</v>
+        <v>0.00507545784985447</v>
       </c>
     </row>
     <row r="20">
@@ -2366,7 +2366,7 @@
         <v>0.0350150955007453</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0420529614264801</v>
+        <v>-0.218516467472156</v>
       </c>
       <c r="I20" t="n">
         <v>-0.0944311286144539</v>
@@ -2414,28 +2414,28 @@
         <v>0.0420686719463712</v>
       </c>
       <c r="X20" t="n">
-        <v>0.612848820878669</v>
+        <v>0.624276286028791</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.117523719448353</v>
+        <v>-0.128951184598474</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.180384979214747</v>
+        <v>0.00433208961806812</v>
       </c>
       <c r="AA20" t="n">
         <v>-0.01888745513281</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.161533192877544</v>
+        <v>-0.0145545091632898</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.274816107829201</v>
+        <v>0.098763218232522</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.65685829430786</v>
+        <v>0.480770592267026</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.279356216210278</v>
+        <v>0.116553190723991</v>
       </c>
     </row>
     <row r="21">
@@ -2461,7 +2461,7 @@
         <v>0.0391411302137562</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0330895642945137</v>
+        <v>-0.219970219961965</v>
       </c>
       <c r="I21" t="n">
         <v>-0.134337351020563</v>
@@ -2509,28 +2509,28 @@
         <v>0.148998237211467</v>
       </c>
       <c r="X21" t="n">
-        <v>0.135250550861866</v>
+        <v>0.145302284954125</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.00375689617678003</v>
+        <v>-0.00629483791547873</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.168699850674615</v>
+        <v>-0.0177897953990833</v>
       </c>
       <c r="AA21" t="n">
         <v>0.234191950358427</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.40248169023671</v>
+        <v>0.216445388165571</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.303037201695179</v>
+        <v>0.11654755562148</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.541489137275356</v>
+        <v>0.355452835204218</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.453520621193276</v>
+        <v>0.279198901152636</v>
       </c>
     </row>
     <row r="22">
@@ -2556,7 +2556,7 @@
         <v>0.056172172525477</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.00295807996764376</v>
+        <v>-0.188746888483817</v>
       </c>
       <c r="I22" t="n">
         <v>-0.115307261317255</v>
@@ -2604,28 +2604,28 @@
         <v>0.000551965031565569</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.18817041587178</v>
+        <v>-0.993610612244152</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.59489256067265</v>
+        <v>0.400332757045023</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.0973949910447126</v>
+        <v>-0.283369016326136</v>
       </c>
       <c r="AA22" t="n">
         <v>0.0253809191774514</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.0719879658795382</v>
+        <v>-0.257912167048449</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0179122702725422</v>
+        <v>-0.168061755008881</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.665265821078667</v>
+        <v>-0.851190022247578</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.218594459309853</v>
+        <v>0.036694984930241</v>
       </c>
     </row>
     <row r="23">
@@ -2651,7 +2651,7 @@
         <v>-0.0393993485224859</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0070494530187146</v>
+        <v>-0.192841980151365</v>
       </c>
       <c r="I23" t="n">
         <v>0.216923374445816</v>
@@ -2699,28 +2699,28 @@
         <v>-0.0299392802978311</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.945848277891172</v>
+        <v>-0.937821968966787</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.540006399170454</v>
+        <v>0.531980090246069</v>
       </c>
       <c r="Z23" t="n">
-        <v>-0.274529505412121</v>
+        <v>-0.475010062638365</v>
       </c>
       <c r="AA23" t="n">
         <v>0.469120272922062</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.00405978308432048</v>
+        <v>-0.203555691108441</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.491452879857937</v>
+        <v>-0.69193343708418</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.409901661805038</v>
+        <v>-0.609397569829158</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0307949871748775</v>
+        <v>-0.156091041151372</v>
       </c>
     </row>
     <row r="24">
@@ -2746,7 +2746,7 @@
         <v>-0.014530714174193</v>
       </c>
       <c r="H24" t="n">
-        <v>0.126456632364786</v>
+        <v>-0.0667857677015623</v>
       </c>
       <c r="I24" t="n">
         <v>0.233931922438709</v>
@@ -2794,28 +2794,28 @@
         <v>0.0465164147221872</v>
       </c>
       <c r="X24" t="n">
-        <v>0.259598704102414</v>
+        <v>0.273885378533513</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.261464773606026</v>
+        <v>-0.275751448037125</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.139229581720164</v>
+        <v>-0.333003537188347</v>
       </c>
       <c r="AA24" t="n">
         <v>0.430455500008955</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.291846132446398</v>
+        <v>0.0989348717429549</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.373161504158873</v>
+        <v>-0.566935459627056</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.289980062942785</v>
+        <v>0.0970688022393427</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.0609245706663911</v>
+        <v>-0.252016488658293</v>
       </c>
     </row>
     <row r="25">
@@ -2835,13 +2835,13 @@
         <v>-0.0733698868603123</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.403643992985071</v>
+        <v>-0.369917954092535</v>
       </c>
       <c r="G25" t="n">
         <v>-0.030262516077315</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0122688877326342</v>
+        <v>0.0123946916539413</v>
       </c>
       <c r="I25" t="n">
         <v>0.142483137788292</v>
@@ -2889,28 +2889,28 @@
         <v>0.0427711776553399</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.59047979678416</v>
+        <v>-1.57957660760554</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.272737134010574</v>
+        <v>0.261833944831957</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.270169588737866</v>
+        <v>-0.236364588453239</v>
       </c>
       <c r="AA25" t="n">
         <v>0.353220653663715</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.0840566015320863</v>
+        <v>0.117735835959556</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.412652726526158</v>
+        <v>-0.378847726241531</v>
       </c>
       <c r="AD25" t="n">
-        <v>-1.2336860612415</v>
+        <v>-1.20000682681403</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.504718370295605</v>
+        <v>-0.640881404162854</v>
       </c>
     </row>
     <row r="26">
@@ -2924,88 +2924,88 @@
         <v>-1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.436508484478446</v>
+        <v>0.444560089981872</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0710580054369052</v>
+        <v>-0.084267853171983</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0501880171233495</v>
+        <v>0.107449703578105</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0586159262003014</v>
+        <v>0.0577769830621507</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0274466981777993</v>
+        <v>0.0278779757243613</v>
       </c>
       <c r="I26" t="n">
-        <v>0.314515777091386</v>
+        <v>0.313969047868496</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0132072895661503</v>
+        <v>0.00704636962286781</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.226200693276775</v>
+        <v>-0.238152185284637</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0403316913163063</v>
+        <v>-0.040176091966644</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.000960782164182661</v>
+        <v>-0.000960168970988708</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.00908597075489488</v>
+        <v>-0.00943337546639562</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.00411399790277102</v>
+        <v>0.00398838007577498</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.00273081610851882</v>
+        <v>-0.00273003823195379</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0146408228761549</v>
+        <v>-0.0146369270637045</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.00724609284152218</v>
+        <v>-0.00724537368698469</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0000696617484409661</v>
+        <v>-0.0000704209155706835</v>
       </c>
       <c r="V26" t="n">
-        <v>0.224985702190415</v>
+        <v>0.220373616310185</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0124692193307716</v>
+        <v>-0.0059703885150818</v>
       </c>
       <c r="X26" t="n">
-        <v>0.299681722190402</v>
+        <v>-0.259566169530045</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.0657687568511386</v>
+        <v>0.619858406339934</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.463404670727734</v>
+        <v>0.513339321470254</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.059175626483968</v>
+        <v>-0.0945012120602486</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.464514269397324</v>
+        <v>0.47934325761517</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.148888893636348</v>
+        <v>0.199370273601759</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.829964748438865</v>
+        <v>0.839635494425059</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.130910727916221</v>
+        <v>-0.218175024994695</v>
       </c>
     </row>
     <row r="27">
@@ -3019,31 +3019,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.246043988517862</v>
+        <v>-0.246246529993399</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.177384890887503</v>
+        <v>-0.177502047951448</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0906545813014853</v>
+        <v>0.12325772030725</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0135823615948663</v>
+        <v>-0.0246042340804182</v>
       </c>
       <c r="H27" t="n">
-        <v>0.150706931921152</v>
+        <v>0.150879703434977</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25154363993049</v>
+        <v>0.251834464025944</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0070302754234444</v>
+        <v>0.00202653012012813</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.281581188453789</v>
+        <v>-0.343380282217703</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0481548133569815</v>
+        <v>-0.027945786423002</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3055,52 +3055,52 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.00932521182800695</v>
+        <v>-0.00929367971980474</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.00643770175100916</v>
+        <v>0.00644514704427025</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.00223511236832679</v>
+        <v>-0.00223769733562764</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.00982172763539681</v>
+        <v>-0.00983308683450656</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.00645843383716623</v>
+        <v>-0.00646590322831928</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.000501429966115183</v>
+        <v>-0.000502009882075564</v>
       </c>
       <c r="V27" t="n">
-        <v>0.207002126874484</v>
+        <v>0.181472014367723</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0365525308670787</v>
+        <v>0.0198469524294004</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.330545226387455</v>
+        <v>-0.567974729331849</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.0928836530179101</v>
+        <v>0.144226151387002</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.485607963229528</v>
+        <v>0.502600841854134</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.0111163549367291</v>
+        <v>-0.191289588691957</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.534548246384224</v>
+        <v>0.372318810025706</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.234064323299038</v>
+        <v>0.25076637782819</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.111119366978859</v>
+        <v>-0.0514297679191404</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.000655470720247145</v>
+        <v>-0.0786830745171904</v>
       </c>
     </row>
     <row r="28">
@@ -3114,31 +3114,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.30586383600656</v>
+        <v>-0.306187967406906</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.176236422781678</v>
+        <v>-0.176352821319061</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0320613916729151</v>
+        <v>0.0559154769853783</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0140897876009744</v>
+        <v>-0.022704116165719</v>
       </c>
       <c r="H28" t="n">
-        <v>0.153541691647888</v>
+        <v>0.153717791033496</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0779306099692082</v>
+        <v>0.0780207296914576</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00575040802720318</v>
+        <v>0.000876639114115922</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0949762773294562</v>
+        <v>-0.152135310829115</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0552129718663187</v>
+        <v>-0.0269586514959123</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3150,52 +3150,52 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.0098190376523815</v>
+        <v>-0.00981494193143837</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.00661357997019864</v>
+        <v>0.00662122866723258</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.00280936961711405</v>
+        <v>-0.00281261873061416</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.00668009000270352</v>
+        <v>-0.00668781574892148</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.00574107447962623</v>
+        <v>-0.00574771421528885</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.000426940925803921</v>
+        <v>-0.000427434693273484</v>
       </c>
       <c r="V28" t="n">
-        <v>0.162758489263254</v>
+        <v>0.137106273050434</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0273760468507932</v>
+        <v>-0.0452687741177263</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.34222721381816</v>
+        <v>-0.320692545073825</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.139873044970078</v>
+        <v>-0.161848243652142</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.255014185511323</v>
+        <v>0.265630291381617</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.0769332529831602</v>
+        <v>-0.105948447441316</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.391740816179884</v>
+        <v>0.219977889128903</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.177083575542115</v>
+        <v>0.187609561690159</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.0903594426083542</v>
+        <v>-0.262562899597064</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.0957403471080321</v>
+        <v>-0.168590999976292</v>
       </c>
     </row>
     <row r="29">
@@ -3209,31 +3209,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.106184459909413</v>
+        <v>-0.106285870650951</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.199946813675512</v>
+        <v>-0.200078872169998</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0227724580374239</v>
+        <v>0.000536223108327645</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00902915102977396</v>
+        <v>-0.0143750862218858</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0174286329701844</v>
+        <v>0.0174474204903091</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0522916142007128</v>
+        <v>-0.0523520946821007</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00661876362926851</v>
+        <v>0.00186033278942525</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0521551690697122</v>
+        <v>-0.0963649832499619</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0596308122823412</v>
+        <v>-0.0286483602459219</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3245,52 +3245,52 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.00933535606876166</v>
+        <v>-0.00933115671243128</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.00912133714131898</v>
+        <v>0.00913188606045454</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.000293043010447602</v>
+        <v>-0.000293381921785515</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.00302862955485382</v>
+        <v>-0.003032132249633</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.00316449350844382</v>
+        <v>-0.00316815333426748</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.000395175505607586</v>
+        <v>-0.000395632535644162</v>
       </c>
       <c r="V29" t="n">
-        <v>0.110150907596729</v>
+        <v>0.0857902637573375</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.0143059554039294</v>
+        <v>-0.0329022460380169</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.165291501850706</v>
+        <v>-0.144265791295202</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.140839771734219</v>
+        <v>-0.162098951525747</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.0600454191026175</v>
+        <v>-0.0468776240724925</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.0962756053700893</v>
+        <v>-0.0791480720390094</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0962912429302152</v>
+        <v>-0.0660648375760431</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.00775380490190472</v>
+        <v>0.00547447060960826</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.20984003065471</v>
+        <v>-0.372429580396992</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.160221160538665</v>
+        <v>0.0383033116279667</v>
       </c>
     </row>
     <row r="30">
@@ -3304,31 +3304,31 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.113238185935717</v>
+        <v>-0.11334633329001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.186214773942108</v>
+        <v>-0.186337762862241</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.291860335754416</v>
+        <v>-0.267629248415259</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00871948653904214</v>
+        <v>-0.0139783969557594</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0273984489695689</v>
+        <v>0.0274288090446067</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.266873947521892</v>
+        <v>-0.267182697935744</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00682585935486931</v>
+        <v>0.0021836715749493</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0447272629054179</v>
+        <v>0.0110472981348585</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0741760058200484</v>
+        <v>-0.0206949803901891</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3340,52 +3340,52 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.00503959208748433</v>
+        <v>-0.00496825694454644</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.00719311552019024</v>
+        <v>0.00720143445149588</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.000285971658178611</v>
+        <v>-0.00028630239121895</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.00134676949436724</v>
+        <v>-0.00134832706755443</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.00177950937707208</v>
+        <v>-0.00178156742611225</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.000365697253103981</v>
+        <v>-0.000366120190757605</v>
       </c>
       <c r="V30" t="n">
-        <v>0.0747691346030732</v>
+        <v>0.0517725184405778</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.00439066643575604</v>
+        <v>-0.00717628862688768</v>
       </c>
       <c r="X30" t="n">
-        <v>-0.159501453782747</v>
+        <v>-0.138693989964264</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.139951506095078</v>
+        <v>-0.160990106187987</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.533901846857373</v>
+        <v>-0.51984196881698</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.187540605958187</v>
+        <v>0.0334113122146709</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.285300702090703</v>
+        <v>-0.426246898977315</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.267027899335481</v>
+        <v>-0.252659270881237</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.584753661968529</v>
+        <v>-0.725930995129566</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.193458442063184</v>
+        <v>-0.353088310760689</v>
       </c>
     </row>
     <row r="31">
@@ -3399,31 +3399,31 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0968978464598438</v>
+        <v>-0.0969903880847796</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.18074145350152</v>
+        <v>-0.180860827468036</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.15535957088525</v>
+        <v>-0.131384247733792</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.00433211445750534</v>
+        <v>-0.00952011195842136</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0343666796632505</v>
+        <v>0.0344051347920768</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.36382241629954</v>
+        <v>-0.364243379873352</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00551495121579593</v>
+        <v>0.000973437841346506</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0136782857117134</v>
+        <v>0.00840309952726774</v>
       </c>
       <c r="L31" t="n">
-        <v>0.00889375869671701</v>
+        <v>-0.0194686981308048</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3435,52 +3435,52 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.00182656494149161</v>
+        <v>-0.0017779828816771</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.00673218956558858</v>
+        <v>0.00673997543443471</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.000279608272315239</v>
+        <v>-0.000279931645926494</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.00101746593741716</v>
+        <v>-0.00101864266220306</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.00149740043885975</v>
+        <v>-0.00149913222094544</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.000318458448563437</v>
+        <v>-0.000318826753313223</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0602510118092915</v>
+        <v>0.0605267521181745</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.0136820299895341</v>
+        <v>-0.0155118321226031</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.14145219263201</v>
+        <v>-0.121186203903832</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.136187107329353</v>
+        <v>-0.156665011648983</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.484036400696089</v>
+        <v>-0.470137339793632</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0709289569975275</v>
+        <v>0.0358113621335527</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.352743017603124</v>
+        <v>-0.374147429438606</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.120213984396549</v>
+        <v>-0.105893959920281</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.630382317564488</v>
+        <v>-0.651998644991421</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.37883386319902</v>
+        <v>-0.50323053002876</v>
       </c>
     </row>
     <row r="32">
@@ -3494,31 +3494,31 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.103480896875323</v>
+        <v>-0.103579725597493</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.188023408655981</v>
+        <v>-0.188147592121669</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0910626909637126</v>
+        <v>0.114183054637327</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.000926599399724825</v>
+        <v>-0.00606810297461049</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0299449975665286</v>
+        <v>0.0299783682547509</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.386429275379733</v>
+        <v>-0.386876409018743</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00526846990965778</v>
+        <v>0.000815610549567348</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0155719571102066</v>
+        <v>-0.0158188891453134</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00934528328550894</v>
+        <v>-0.0190001177249655</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3530,52 +3530,52 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.000352838956830397</v>
+        <v>0.000353914684473049</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.00623065664900438</v>
+        <v>0.00623786249287964</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.000274164577999679</v>
+        <v>-0.000274481655876253</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.00100120816583779</v>
+        <v>-0.00100236608809149</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.00123761106939872</v>
+        <v>-0.00123904239793884</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.000312156590467466</v>
+        <v>-0.000312517607016392</v>
       </c>
       <c r="V32" t="n">
-        <v>0.00927619585602209</v>
+        <v>0.0102429996730462</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.0235736253118514</v>
+        <v>-0.0243680184013916</v>
       </c>
       <c r="X32" t="n">
-        <v>-0.146342953199862</v>
+        <v>-0.126639213309576</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.145161352331443</v>
+        <v>-0.165088104409586</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.260600449467441</v>
+        <v>-0.247426180026452</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.0143824450603608</v>
+        <v>-0.0451843112530229</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.246178240510729</v>
+        <v>-0.292728985472978</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.125828825912292</v>
+        <v>0.139450228992291</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.537682546042034</v>
+        <v>-0.584456303192139</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.49066463905744</v>
+        <v>-0.583703880927529</v>
       </c>
     </row>
     <row r="33">
@@ -3589,31 +3589,31 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.170883303356563</v>
+        <v>-0.171046504285632</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.184495417794735</v>
+        <v>-0.18461727113496</v>
       </c>
       <c r="F33" t="n">
-        <v>0.128834675525228</v>
+        <v>0.136402092765251</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0107213802706063</v>
+        <v>0.00564313675098016</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0347622944157237</v>
+        <v>0.0348012655875945</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.42871696202656</v>
+        <v>-0.429213053195863</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00628379817755373</v>
+        <v>0.00192108460367546</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0195741899100774</v>
+        <v>-0.0197448237226584</v>
       </c>
       <c r="L33" t="n">
-        <v>0.00975507824660246</v>
+        <v>-0.018527409759667</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3625,52 +3625,52 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00248763586780503</v>
+        <v>0.00250329316170348</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0085490132088127</v>
+        <v>0.00855890023604945</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000198300178911062</v>
+        <v>0.000198529517719859</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.000992810208750326</v>
+        <v>-0.0009939584185111</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.000239999786936005</v>
+        <v>-0.000240277352383458</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.000305491844496977</v>
+        <v>-0.000305845153127051</v>
       </c>
       <c r="V33" t="n">
-        <v>0.053919384396431</v>
+        <v>0.0550834289509777</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.0116002414147659</v>
+        <v>-0.0112608000960554</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.212317363109721</v>
+        <v>-0.193154801650048</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.143061358041577</v>
+        <v>-0.162508973770544</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.247370645122349</v>
+        <v>-0.249695769869229</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0422063479452472</v>
+        <v>0.0152909029347207</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.205053392260878</v>
+        <v>-0.234364347345436</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.181346316904211</v>
+        <v>0.179517283326634</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.560432113412177</v>
+        <v>-0.590028122766028</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.578312659746807</v>
+        <v>-0.638103516519787</v>
       </c>
     </row>
     <row r="34">
@@ -3684,31 +3684,31 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.203814322711313</v>
+        <v>-0.204008974184984</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.183578043716544</v>
+        <v>-0.183699291160444</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0139896774285151</v>
+        <v>-0.0137132938211029</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00704988013781239</v>
+        <v>0.00410005871977225</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0165231528905049</v>
+        <v>0.0165410570776534</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.616876171778661</v>
+        <v>-0.617590161604005</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0103444268268873</v>
+        <v>0.00607362758629908</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0919261259634657</v>
+        <v>-0.112629664386606</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0101430800572218</v>
+        <v>-0.0181169385357897</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3720,52 +3720,52 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.00208389012354234</v>
+        <v>0.00213487577351272</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.00342021698030483</v>
+        <v>0.00342417252441635</v>
       </c>
       <c r="R34" t="n">
-        <v>0.000194363861199969</v>
+        <v>0.000194588647553146</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.000995798705676766</v>
+        <v>-0.000996950371730392</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.000299428155345378</v>
+        <v>-0.000299774451181366</v>
       </c>
       <c r="V34" t="n">
-        <v>0.0766169548053737</v>
+        <v>0.077764056217266</v>
       </c>
       <c r="W34" t="n">
-        <v>0.00776090067773104</v>
+        <v>0.0094510056392769</v>
       </c>
       <c r="X34" t="n">
-        <v>-0.244211244253022</v>
+        <v>-0.225455437068654</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.143181122174836</v>
+        <v>-0.162252828276773</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.59681672518361</v>
+        <v>-0.604501734527056</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.00707479084738743</v>
+        <v>-0.0389810176841416</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.589697129248894</v>
+        <v>-0.643732556992063</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.0200594465950505</v>
+        <v>0.0130884270769487</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.977089495676752</v>
+        <v>-1.03144082233749</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.676396618173863</v>
+        <v>-0.714480973321769</v>
       </c>
     </row>
   </sheetData>
